--- a/docs/pruefberichte/2026-10-22-arbeitsschutz-pruefergebnis-umsetzung.xlsx
+++ b/docs/pruefberichte/2026-10-22-arbeitsschutz-pruefergebnis-umsetzung.xlsx
@@ -18537,7 +18537,7 @@
       </c>
       <c r="G8" s="27" t="inlineStr">
         <is>
-          <t>Hinweis im Abschnitt Mutterschutz (§§ 9–12 MuSchG); Warnung bei „keine Schutzmaßnahmen“ um Biostoffe, Heben/Tragen, Strahlung erweitert.</t>
+          <t>Hinweis im Abschnitt Mutterschutz (§§ 9–12 MuSchG); Warnung bei „keine Schutzmaßnahmen“ um Biostoffe, Heben/Tragen, Strahlung erweitert. Fundstelle nach Rückmeldung 22.10.2026: § 14 Abs. 3 BioStoffV.</t>
         </is>
       </c>
     </row>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="G10" s="27" t="inlineStr">
         <is>
-          <t>Gefahr-/Biostoff-Themen: Kasten „Unterschriften auf Papier nötig“, „Alle Pflichtangaben“ erst nach „Unterschriften auf Papier eingeholt“, PDF mit Hinweis und Unterschriftsspalte. Handschriftliche Signatur am Gerät nicht gebaut – nur Papier, bis die rechtliche Bewertung vorliegt (T-154).</t>
+          <t>Gefahr-/Biostoff-Themen: Kasten „Unterschriften auf Papier nötig“, „Alle Pflichtangaben“ erst nach „Unterschriften auf Papier eingeholt“, PDF mit Hinweis und Unterschriftsspalte. Handschriftliche Signatur am Gerät nicht gebaut – nur Papier, bis die rechtliche Bewertung vorliegt (T-154). Fundstelle nach Rückmeldung 22.10.2026: § 14 Abs. 3 BioStoffV.</t>
         </is>
       </c>
     </row>
@@ -18759,7 +18759,7 @@
       </c>
       <c r="G14" s="27" t="inlineStr">
         <is>
-          <t>Neue Vorlagen „Betriebsanweisung Maschinen“ (betriebsanweisung_maschine, § 12 BetrSichV, Vorschläge für Aufschnitt-, Knetmaschine, Kreissäge, Hebebühne, Reifenmontiermaschine) und „Betriebsanweisung Biostoffe“ (betriebsanweisung_biostoffe, § 14 BioStoffV).</t>
+          <t>Neue Vorlagen „Betriebsanweisung Maschinen“ (betriebsanweisung_maschine, § 12 BetrSichV, Vorschläge für Aufschnitt-, Knetmaschine, Kreissäge, Hebebühne, Reifenmontiermaschine) und „Betriebsanweisung Biostoffe“ (betriebsanweisung_biostoffe, § 14 BioStoffV). Fundstelle nach Rückmeldung 22.10.2026: § 14 Abs. 3 BioStoffV.</t>
         </is>
       </c>
     </row>
@@ -21096,7 +21096,7 @@
           <t>umgesetzt</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>neu arbeitsschutz.erste_hilfe_organisation (§§ 24, 25 DGUV V1, ASR A4.3).</t>
         </is>
@@ -21123,7 +21123,7 @@
           <t>umgesetzt</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>neu arbeitsschutz.brandschutzhelfer (ASR A2.2 Abschn. 7.3, 5 %, § 10 Abs. 2 ArbSchG).</t>
         </is>
@@ -21150,7 +21150,7 @@
           <t>umgesetzt</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>neu arbeitsschutz.flucht_rettungsplan (§ 4 Abs. 4 ArbStättV, ASR A2.3) als Hinweis.</t>
         </is>
@@ -21177,7 +21177,7 @@
           <t>umgesetzt</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>neu arbeitsschutz.expositionsverzeichnis (§ 10a GefStoffV, 40/5 Jahre, ZED) als Hinweis für Handwerk/Bau mit Gefahrstoffen</t>
         </is>
@@ -21204,7 +21204,7 @@
           <t>umgesetzt</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>neu arbeitsschutz.betriebsanweisung_arbeitsmittel (§ 12 BetrSichV) für Branchen mit Maschinen</t>
         </is>
@@ -21231,7 +21231,7 @@
           <t>umgesetzt</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>neu arbeitsschutz.biostoffe (§§ 4, 7, 14 BioStoffV) für Praxis, Kosmetik, Gebäudereinigung</t>
         </is>
@@ -21258,7 +21258,7 @@
           <t>umgesetzt</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>neu arbeitsschutz.laerm (LärmVibrationsArbSchV) als Hinweis für Handwerk/Bau.</t>
         </is>
@@ -21285,7 +21285,7 @@
           <t>umgesetzt</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>neu arbeitsschutz.verbandbuch (§ 24 Abs. 6 DGUV V1) je gemeldetem Unfall.</t>
         </is>
@@ -21312,7 +21312,7 @@
           <t>abweichend umgesetzt</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>in arbeitsschutz.arbeitsmittel_pruefen aufgenommen (Auslöser alle Betriebe mit Beschäftigten), keine eigene Pflicht.</t>
         </is>
@@ -21339,7 +21339,7 @@
           <t>umgesetzt</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>neu arbeitsschutz.sicherheitsbeauftragte (§ 22 SGB VII n. F., anzuwenden ab 29.5.2026</t>
         </is>
@@ -21366,7 +21366,7 @@
           <t>umgesetzt</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>neu branche.gastro_schankanlage_fluessiggas (BetrSichV, DGUV R 110-007, DGUV V79) als Hinweis für Gastronomie.</t>
         </is>
@@ -21393,7 +21393,7 @@
           <t>umgesetzt</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>neu arbeitsschutz.fremdfirmen_abstimmung (§ 8 ArbSchG, §§ 5, 6 DGUV V1) für Handwerk/Bau/Reinigung oder Vertrieb vor Ort.</t>
         </is>
